--- a/refactored/projects/erpt/data/data_erpt_aa.xlsx
+++ b/refactored/projects/erpt/data/data_erpt_aa.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cristhianlarrahondo/Documents/GitHub/svartoolkit/refactored/projects/erpt/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B914DF9-2A10-D148-9AEE-C11373635296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458E305C-52ED-F24E-B865-CF89E9B7A1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="1160" windowWidth="27640" windowHeight="16660" activeTab="1" xr2:uid="{5D711EF9-1BBE-F74F-B682-3DB468C674F3}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
-    <sheet name="metada" sheetId="2" r:id="rId2"/>
+    <sheet name="metadata" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
